--- a/artfynd/A 64817-2023 artfynd.xlsx
+++ b/artfynd/A 64817-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118927329</v>
+        <v>118925679</v>
       </c>
       <c r="B2" t="n">
-        <v>77423</v>
+        <v>90529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624174</v>
+        <v>624112</v>
       </c>
       <c r="R2" t="n">
-        <v>7306885</v>
+        <v>7306697</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,26 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118927351</v>
+        <v>118926458</v>
       </c>
       <c r="B3" t="n">
-        <v>79080</v>
+        <v>90525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624174</v>
+        <v>624138</v>
       </c>
       <c r="R3" t="n">
-        <v>7306885</v>
+        <v>7306761</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,6 +863,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118926932</v>
+        <v>118927143</v>
       </c>
       <c r="B4" t="n">
-        <v>90437</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624112</v>
+        <v>624210</v>
       </c>
       <c r="R4" t="n">
-        <v>7306964</v>
+        <v>7306965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,26 +990,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118927553</v>
+        <v>118925866</v>
       </c>
       <c r="B5" t="n">
-        <v>90529</v>
+        <v>78573</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624179</v>
+        <v>624097</v>
       </c>
       <c r="R5" t="n">
-        <v>7306747</v>
+        <v>7306720</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,6 +1092,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118925102</v>
+        <v>118925261</v>
       </c>
       <c r="B6" t="n">
-        <v>79073</v>
+        <v>90529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624207</v>
+        <v>624125</v>
       </c>
       <c r="R6" t="n">
-        <v>7306638</v>
+        <v>7306711</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,26 +1214,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1245,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118926450</v>
+        <v>118927329</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>77423</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1246,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624139</v>
+        <v>624174</v>
       </c>
       <c r="R7" t="n">
-        <v>7306755</v>
+        <v>7306885</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,6 +1316,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118927701</v>
+        <v>118926360</v>
       </c>
       <c r="B8" t="n">
-        <v>90565</v>
+        <v>104932</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,25 +1364,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3277</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624205</v>
+        <v>624137</v>
       </c>
       <c r="R8" t="n">
-        <v>7306715</v>
+        <v>7306757</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118927732</v>
+        <v>118926047</v>
       </c>
       <c r="B9" t="n">
-        <v>91288</v>
+        <v>82270</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,25 +1466,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>918</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624261</v>
+        <v>624098</v>
       </c>
       <c r="R9" t="n">
-        <v>7306731</v>
+        <v>7306733</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,26 +1540,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1576,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118927645</v>
+        <v>118927118</v>
       </c>
       <c r="B10" t="n">
-        <v>90529</v>
+        <v>90437</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624195</v>
+        <v>624237</v>
       </c>
       <c r="R10" t="n">
-        <v>7306733</v>
+        <v>7306993</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118925633</v>
+        <v>118927078</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>90529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,25 +1670,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624087</v>
+        <v>624160</v>
       </c>
       <c r="R11" t="n">
-        <v>7306680</v>
+        <v>7306966</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118926148</v>
+        <v>118926173</v>
       </c>
       <c r="B12" t="n">
-        <v>5166</v>
+        <v>74603</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,25 +1772,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1820,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624103</v>
+        <v>624111</v>
       </c>
       <c r="R12" t="n">
-        <v>7306727</v>
+        <v>7306730</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1866,26 +1846,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Under bark på död ved</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Under bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1902,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118927143</v>
+        <v>118925785</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
+        <v>79572</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,39 +1878,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624210</v>
+        <v>624100</v>
       </c>
       <c r="R13" t="n">
-        <v>7306965</v>
+        <v>7306706</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,6 +1948,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2009,7 +1984,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118925261</v>
+        <v>118927591</v>
       </c>
       <c r="B14" t="n">
         <v>90529</v>
@@ -2049,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624125</v>
+        <v>624178</v>
       </c>
       <c r="R14" t="n">
-        <v>7306711</v>
+        <v>7306745</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118925162</v>
+        <v>118927553</v>
       </c>
       <c r="B15" t="n">
-        <v>90522</v>
+        <v>90529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624198</v>
+        <v>624179</v>
       </c>
       <c r="R15" t="n">
-        <v>7306606</v>
+        <v>7306747</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118926360</v>
+        <v>118926111</v>
       </c>
       <c r="B16" t="n">
-        <v>104932</v>
+        <v>57306</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2225,38 +2200,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624137</v>
+        <v>624121</v>
       </c>
       <c r="R16" t="n">
-        <v>7306757</v>
+        <v>7306730</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118926111</v>
+        <v>118925102</v>
       </c>
       <c r="B17" t="n">
-        <v>57306</v>
+        <v>79080</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2331,39 +2311,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624121</v>
+        <v>624207</v>
       </c>
       <c r="R17" t="n">
-        <v>7306730</v>
+        <v>7306638</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,6 +2381,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2422,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118926458</v>
+        <v>118927259</v>
       </c>
       <c r="B18" t="n">
-        <v>90525</v>
+        <v>90476</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2434,25 +2429,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624138</v>
+        <v>624213</v>
       </c>
       <c r="R18" t="n">
-        <v>7306761</v>
+        <v>7306954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,12 +2506,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -2526,7 +2521,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2544,7 +2539,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118925679</v>
+        <v>118927041</v>
       </c>
       <c r="B19" t="n">
         <v>90529</v>
@@ -2584,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624112</v>
+        <v>624109</v>
       </c>
       <c r="R19" t="n">
-        <v>7306697</v>
+        <v>7306964</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2646,10 +2641,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118925785</v>
+        <v>118927219</v>
       </c>
       <c r="B20" t="n">
-        <v>79572</v>
+        <v>90529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2662,21 +2657,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2686,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624100</v>
+        <v>624245</v>
       </c>
       <c r="R20" t="n">
-        <v>7306706</v>
+        <v>7306978</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,26 +2727,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2768,10 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118926826</v>
+        <v>118925708</v>
       </c>
       <c r="B21" t="n">
-        <v>79109</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2780,25 +2755,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624134</v>
+        <v>624120</v>
       </c>
       <c r="R21" t="n">
-        <v>7306829</v>
+        <v>7306680</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2854,6 +2829,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2870,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118927605</v>
+        <v>118926450</v>
       </c>
       <c r="B22" t="n">
-        <v>79109</v>
+        <v>57290</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2886,34 +2881,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624181</v>
+        <v>624139</v>
       </c>
       <c r="R22" t="n">
-        <v>7306734</v>
+        <v>7306755</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118925978</v>
+        <v>118925985</v>
       </c>
       <c r="B23" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2988,29 +2988,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
@@ -3079,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118925929</v>
+        <v>118926826</v>
       </c>
       <c r="B24" t="n">
-        <v>74603</v>
+        <v>79109</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3095,21 +3090,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3119,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624109</v>
+        <v>624134</v>
       </c>
       <c r="R24" t="n">
-        <v>7306708</v>
+        <v>7306829</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3165,26 +3160,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3201,10 +3176,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118926687</v>
+        <v>118927701</v>
       </c>
       <c r="B25" t="n">
-        <v>82270</v>
+        <v>90565</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3217,21 +3192,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>3277</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3241,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624121</v>
+        <v>624205</v>
       </c>
       <c r="R25" t="n">
-        <v>7306811</v>
+        <v>7306715</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3303,10 +3278,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118924931</v>
+        <v>118925978</v>
       </c>
       <c r="B26" t="n">
-        <v>79102</v>
+        <v>57290</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3319,34 +3294,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624243</v>
+        <v>624097</v>
       </c>
       <c r="R26" t="n">
-        <v>7306648</v>
+        <v>7306712</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3389,26 +3369,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3425,10 +3385,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118925708</v>
+        <v>118926687</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>82270</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3437,25 +3397,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3465,10 +3425,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>624120</v>
+        <v>624121</v>
       </c>
       <c r="R27" t="n">
-        <v>7306680</v>
+        <v>7306811</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3511,26 +3471,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3547,10 +3487,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118926697</v>
+        <v>118926085</v>
       </c>
       <c r="B28" t="n">
-        <v>78491</v>
+        <v>90529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3563,21 +3503,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3587,10 +3527,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>624122</v>
+        <v>624103</v>
       </c>
       <c r="R28" t="n">
-        <v>7306805</v>
+        <v>7306730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3649,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118927259</v>
+        <v>118926985</v>
       </c>
       <c r="B29" t="n">
-        <v>90476</v>
+        <v>78491</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3661,25 +3601,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3689,10 +3629,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>624213</v>
+        <v>624122</v>
       </c>
       <c r="R29" t="n">
-        <v>7306954</v>
+        <v>7306979</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3735,26 +3675,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3771,10 +3691,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118927219</v>
+        <v>118926947</v>
       </c>
       <c r="B30" t="n">
-        <v>90529</v>
+        <v>78136</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3787,21 +3707,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3811,10 +3731,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>624245</v>
+        <v>624110</v>
       </c>
       <c r="R30" t="n">
-        <v>7306978</v>
+        <v>7306963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3857,6 +3777,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3873,10 +3813,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118927041</v>
+        <v>118925874</v>
       </c>
       <c r="B31" t="n">
-        <v>90529</v>
+        <v>82270</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3889,21 +3829,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3913,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>624109</v>
+        <v>624111</v>
       </c>
       <c r="R31" t="n">
-        <v>7306964</v>
+        <v>7306711</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3959,6 +3899,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3975,10 +3935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118926985</v>
+        <v>118925929</v>
       </c>
       <c r="B32" t="n">
-        <v>78491</v>
+        <v>74603</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3991,21 +3951,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4015,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>624122</v>
+        <v>624109</v>
       </c>
       <c r="R32" t="n">
-        <v>7306979</v>
+        <v>7306708</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4061,6 +4021,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4077,10 +4057,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118925866</v>
+        <v>118927645</v>
       </c>
       <c r="B33" t="n">
-        <v>78573</v>
+        <v>90529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4093,21 +4073,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4117,10 +4097,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>624097</v>
+        <v>624195</v>
       </c>
       <c r="R33" t="n">
-        <v>7306720</v>
+        <v>7306733</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4163,26 +4143,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4199,10 +4159,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118925874</v>
+        <v>118925162</v>
       </c>
       <c r="B34" t="n">
-        <v>82270</v>
+        <v>90529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4215,21 +4175,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4239,10 +4199,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>624111</v>
+        <v>624198</v>
       </c>
       <c r="R34" t="n">
-        <v>7306711</v>
+        <v>7306606</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4285,26 +4245,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4321,10 +4261,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118926332</v>
+        <v>118926148</v>
       </c>
       <c r="B35" t="n">
-        <v>57290</v>
+        <v>5166</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4333,43 +4273,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>624131</v>
+        <v>624103</v>
       </c>
       <c r="R35" t="n">
-        <v>7306764</v>
+        <v>7306727</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4412,6 +4347,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Under bark på död ved</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Under bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4428,10 +4383,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118926085</v>
+        <v>118924931</v>
       </c>
       <c r="B36" t="n">
-        <v>90529</v>
+        <v>79109</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4444,21 +4399,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4468,10 +4423,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>624103</v>
+        <v>624243</v>
       </c>
       <c r="R36" t="n">
-        <v>7306730</v>
+        <v>7306648</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4514,6 +4469,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4530,10 +4505,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118927825</v>
+        <v>118927732</v>
       </c>
       <c r="B37" t="n">
-        <v>90529</v>
+        <v>91288</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4542,25 +4517,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4570,10 +4545,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>624272</v>
+        <v>624261</v>
       </c>
       <c r="R37" t="n">
-        <v>7306822</v>
+        <v>7306731</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4616,6 +4591,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4632,10 +4627,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118926894</v>
+        <v>118926301</v>
       </c>
       <c r="B38" t="n">
-        <v>79109</v>
+        <v>77428</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4648,21 +4643,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4672,10 +4667,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>624140</v>
+        <v>624125</v>
       </c>
       <c r="R38" t="n">
-        <v>7306929</v>
+        <v>7306753</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4718,6 +4713,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4734,10 +4749,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118927118</v>
+        <v>118926894</v>
       </c>
       <c r="B39" t="n">
-        <v>90437</v>
+        <v>79109</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4750,21 +4765,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4774,10 +4789,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>624237</v>
+        <v>624140</v>
       </c>
       <c r="R39" t="n">
-        <v>7306993</v>
+        <v>7306929</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4836,10 +4851,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118926947</v>
+        <v>118927605</v>
       </c>
       <c r="B40" t="n">
-        <v>78136</v>
+        <v>79109</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4852,21 +4867,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4876,10 +4891,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>624110</v>
+        <v>624181</v>
       </c>
       <c r="R40" t="n">
-        <v>7306963</v>
+        <v>7306734</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4922,26 +4937,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4958,10 +4953,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118927078</v>
+        <v>118927009</v>
       </c>
       <c r="B41" t="n">
-        <v>90529</v>
+        <v>74603</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4974,21 +4969,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4998,10 +4993,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>624160</v>
+        <v>624137</v>
       </c>
       <c r="R41" t="n">
-        <v>7306966</v>
+        <v>7306972</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5060,10 +5055,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118927009</v>
+        <v>118927825</v>
       </c>
       <c r="B42" t="n">
-        <v>74603</v>
+        <v>90529</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5076,21 +5071,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5100,10 +5095,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>624137</v>
+        <v>624272</v>
       </c>
       <c r="R42" t="n">
-        <v>7306972</v>
+        <v>7306822</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5162,10 +5157,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118925985</v>
+        <v>118926932</v>
       </c>
       <c r="B43" t="n">
-        <v>90529</v>
+        <v>90437</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5178,21 +5173,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>3242</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5202,10 +5197,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>624097</v>
+        <v>624112</v>
       </c>
       <c r="R43" t="n">
-        <v>7306712</v>
+        <v>7306964</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5248,6 +5243,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5264,10 +5279,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118926301</v>
+        <v>118927343</v>
       </c>
       <c r="B44" t="n">
-        <v>77428</v>
+        <v>77875</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5280,21 +5295,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5304,10 +5319,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>624125</v>
+        <v>624174</v>
       </c>
       <c r="R44" t="n">
-        <v>7306753</v>
+        <v>7306885</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5353,22 +5368,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5386,10 +5401,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118927343</v>
+        <v>118926697</v>
       </c>
       <c r="B45" t="n">
-        <v>77875</v>
+        <v>78491</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5402,21 +5417,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5426,10 +5441,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>624174</v>
+        <v>624122</v>
       </c>
       <c r="R45" t="n">
-        <v>7306885</v>
+        <v>7306805</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5472,26 +5487,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5508,10 +5503,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118927591</v>
+        <v>118927351</v>
       </c>
       <c r="B46" t="n">
-        <v>90529</v>
+        <v>79080</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5524,21 +5519,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5548,10 +5543,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>624178</v>
+        <v>624174</v>
       </c>
       <c r="R46" t="n">
-        <v>7306745</v>
+        <v>7306885</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5610,10 +5605,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118926047</v>
+        <v>118926332</v>
       </c>
       <c r="B47" t="n">
-        <v>82270</v>
+        <v>57290</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5626,34 +5621,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>624098</v>
+        <v>624131</v>
       </c>
       <c r="R47" t="n">
-        <v>7306733</v>
+        <v>7306764</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5712,10 +5712,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118926173</v>
+        <v>118925633</v>
       </c>
       <c r="B48" t="n">
-        <v>74603</v>
+        <v>79476</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5724,25 +5724,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5752,10 +5752,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>624111</v>
+        <v>624087</v>
       </c>
       <c r="R48" t="n">
-        <v>7306730</v>
+        <v>7306680</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 64817-2023 artfynd.xlsx
+++ b/artfynd/A 64817-2023 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118927143</v>
+        <v>118925866</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>78573</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624210</v>
+        <v>624097</v>
       </c>
       <c r="R4" t="n">
-        <v>7306965</v>
+        <v>7306720</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,6 +985,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1006,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118925866</v>
+        <v>118925261</v>
       </c>
       <c r="B5" t="n">
-        <v>78573</v>
+        <v>90529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624097</v>
+        <v>624125</v>
       </c>
       <c r="R5" t="n">
-        <v>7306720</v>
+        <v>7306711</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,26 +1107,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118925261</v>
+        <v>118927143</v>
       </c>
       <c r="B6" t="n">
-        <v>90529</v>
+        <v>57290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1139,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624125</v>
+        <v>624210</v>
       </c>
       <c r="R6" t="n">
-        <v>7306711</v>
+        <v>7306965</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118927118</v>
+        <v>118926173</v>
       </c>
       <c r="B10" t="n">
-        <v>90437</v>
+        <v>74603</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3242</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624237</v>
+        <v>624111</v>
       </c>
       <c r="R10" t="n">
-        <v>7306993</v>
+        <v>7306730</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118927078</v>
+        <v>118927118</v>
       </c>
       <c r="B11" t="n">
-        <v>90529</v>
+        <v>90437</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624160</v>
+        <v>624237</v>
       </c>
       <c r="R11" t="n">
-        <v>7306966</v>
+        <v>7306993</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118926173</v>
+        <v>118927078</v>
       </c>
       <c r="B12" t="n">
-        <v>74603</v>
+        <v>90529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624111</v>
+        <v>624160</v>
       </c>
       <c r="R12" t="n">
-        <v>7306730</v>
+        <v>7306966</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118925785</v>
+        <v>118927591</v>
       </c>
       <c r="B13" t="n">
-        <v>79572</v>
+        <v>90529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624100</v>
+        <v>624178</v>
       </c>
       <c r="R13" t="n">
-        <v>7306706</v>
+        <v>7306745</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,26 +1948,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1984,7 +1964,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118927591</v>
+        <v>118927553</v>
       </c>
       <c r="B14" t="n">
         <v>90529</v>
@@ -2024,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624178</v>
+        <v>624179</v>
       </c>
       <c r="R14" t="n">
-        <v>7306745</v>
+        <v>7306747</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118927553</v>
+        <v>118925785</v>
       </c>
       <c r="B15" t="n">
-        <v>90529</v>
+        <v>79572</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,21 +2082,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2126,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624179</v>
+        <v>624100</v>
       </c>
       <c r="R15" t="n">
-        <v>7306747</v>
+        <v>7306706</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,6 +2152,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118927259</v>
+        <v>118926450</v>
       </c>
       <c r="B18" t="n">
-        <v>90476</v>
+        <v>57290</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2429,38 +2429,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624213</v>
+        <v>624139</v>
       </c>
       <c r="R18" t="n">
-        <v>7306954</v>
+        <v>7306755</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2503,26 +2508,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2539,7 +2524,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118927041</v>
+        <v>118925985</v>
       </c>
       <c r="B19" t="n">
         <v>90529</v>
@@ -2579,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624109</v>
+        <v>624097</v>
       </c>
       <c r="R19" t="n">
-        <v>7306964</v>
+        <v>7306712</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2641,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118927219</v>
+        <v>118927259</v>
       </c>
       <c r="B20" t="n">
-        <v>90529</v>
+        <v>90476</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2653,25 +2638,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2681,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624245</v>
+        <v>624213</v>
       </c>
       <c r="R20" t="n">
-        <v>7306978</v>
+        <v>7306954</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2727,6 +2712,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2743,10 +2748,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118925708</v>
+        <v>118927041</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>90529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2755,25 +2760,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2783,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624120</v>
+        <v>624109</v>
       </c>
       <c r="R21" t="n">
-        <v>7306680</v>
+        <v>7306964</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2829,26 +2834,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2865,10 +2850,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118926450</v>
+        <v>118927219</v>
       </c>
       <c r="B22" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2881,39 +2866,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624139</v>
+        <v>624245</v>
       </c>
       <c r="R22" t="n">
-        <v>7306755</v>
+        <v>7306978</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2972,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118925985</v>
+        <v>118925708</v>
       </c>
       <c r="B23" t="n">
-        <v>90529</v>
+        <v>79607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2984,25 +2964,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3012,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624097</v>
+        <v>624120</v>
       </c>
       <c r="R23" t="n">
-        <v>7306712</v>
+        <v>7306680</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3058,6 +3038,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118926985</v>
+        <v>118925874</v>
       </c>
       <c r="B29" t="n">
-        <v>78491</v>
+        <v>82270</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3605,21 +3605,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>624122</v>
+        <v>624111</v>
       </c>
       <c r="R29" t="n">
-        <v>7306979</v>
+        <v>7306711</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,6 +3675,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3691,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118926947</v>
+        <v>118925929</v>
       </c>
       <c r="B30" t="n">
-        <v>78136</v>
+        <v>74603</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3707,21 +3727,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,10 +3751,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>624110</v>
+        <v>624109</v>
       </c>
       <c r="R30" t="n">
-        <v>7306963</v>
+        <v>7306708</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3780,22 +3800,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3813,10 +3833,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118925874</v>
+        <v>118926985</v>
       </c>
       <c r="B31" t="n">
-        <v>82270</v>
+        <v>78491</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3829,21 +3849,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3853,10 +3873,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>624111</v>
+        <v>624122</v>
       </c>
       <c r="R31" t="n">
-        <v>7306711</v>
+        <v>7306979</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3899,26 +3919,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3935,10 +3935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118925929</v>
+        <v>118926947</v>
       </c>
       <c r="B32" t="n">
-        <v>74603</v>
+        <v>78136</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>624109</v>
+        <v>624110</v>
       </c>
       <c r="R32" t="n">
-        <v>7306708</v>
+        <v>7306963</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,22 +4024,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5605,10 +5605,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118926332</v>
+        <v>118925633</v>
       </c>
       <c r="B47" t="n">
-        <v>57290</v>
+        <v>79476</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,43 +5617,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>624131</v>
+        <v>624087</v>
       </c>
       <c r="R47" t="n">
-        <v>7306764</v>
+        <v>7306680</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5712,10 +5707,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118925633</v>
+        <v>118926332</v>
       </c>
       <c r="B48" t="n">
-        <v>79476</v>
+        <v>57290</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5724,38 +5719,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>624087</v>
+        <v>624131</v>
       </c>
       <c r="R48" t="n">
-        <v>7306680</v>
+        <v>7306764</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 64817-2023 artfynd.xlsx
+++ b/artfynd/A 64817-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118925679</v>
+        <v>118927825</v>
       </c>
       <c r="B2" t="n">
         <v>90529</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624112</v>
+        <v>624272</v>
       </c>
       <c r="R2" t="n">
-        <v>7306697</v>
+        <v>7306822</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118926458</v>
+        <v>118927041</v>
       </c>
       <c r="B3" t="n">
-        <v>90525</v>
+        <v>90529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624138</v>
+        <v>624109</v>
       </c>
       <c r="R3" t="n">
-        <v>7306761</v>
+        <v>7306964</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,26 +863,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118925866</v>
+        <v>118925261</v>
       </c>
       <c r="B4" t="n">
-        <v>78573</v>
+        <v>90529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624097</v>
+        <v>624125</v>
       </c>
       <c r="R4" t="n">
-        <v>7306720</v>
+        <v>7306711</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,26 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118925261</v>
+        <v>118926687</v>
       </c>
       <c r="B5" t="n">
-        <v>90529</v>
+        <v>82270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624125</v>
+        <v>624121</v>
       </c>
       <c r="R5" t="n">
-        <v>7306711</v>
+        <v>7306811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118927143</v>
+        <v>118925866</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>78573</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,39 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624210</v>
+        <v>624097</v>
       </c>
       <c r="R6" t="n">
-        <v>7306965</v>
+        <v>7306720</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,6 +1169,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1230,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118927329</v>
+        <v>118925679</v>
       </c>
       <c r="B7" t="n">
-        <v>77423</v>
+        <v>90529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624174</v>
+        <v>624112</v>
       </c>
       <c r="R7" t="n">
-        <v>7306885</v>
+        <v>7306697</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,26 +1291,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1352,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118926360</v>
+        <v>118927645</v>
       </c>
       <c r="B8" t="n">
-        <v>104932</v>
+        <v>90529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624137</v>
+        <v>624195</v>
       </c>
       <c r="R8" t="n">
-        <v>7306757</v>
+        <v>7306733</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118926047</v>
+        <v>118927343</v>
       </c>
       <c r="B9" t="n">
-        <v>82270</v>
+        <v>77875</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624098</v>
+        <v>624174</v>
       </c>
       <c r="R9" t="n">
-        <v>7306733</v>
+        <v>7306885</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,6 +1495,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1556,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118926173</v>
+        <v>118926360</v>
       </c>
       <c r="B10" t="n">
-        <v>74603</v>
+        <v>104932</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,25 +1543,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624111</v>
+        <v>624137</v>
       </c>
       <c r="R10" t="n">
-        <v>7306730</v>
+        <v>7306757</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118927118</v>
+        <v>118927259</v>
       </c>
       <c r="B11" t="n">
-        <v>90437</v>
+        <v>90476</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,25 +1645,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624237</v>
+        <v>624213</v>
       </c>
       <c r="R11" t="n">
-        <v>7306993</v>
+        <v>7306954</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,6 +1719,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1760,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118927078</v>
+        <v>118925874</v>
       </c>
       <c r="B12" t="n">
-        <v>90529</v>
+        <v>82270</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624160</v>
+        <v>624111</v>
       </c>
       <c r="R12" t="n">
-        <v>7306966</v>
+        <v>7306711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,6 +1841,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1862,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118927591</v>
+        <v>118927605</v>
       </c>
       <c r="B13" t="n">
-        <v>90529</v>
+        <v>79109</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,21 +1893,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624178</v>
+        <v>624181</v>
       </c>
       <c r="R13" t="n">
-        <v>7306745</v>
+        <v>7306734</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118927553</v>
+        <v>118926148</v>
       </c>
       <c r="B14" t="n">
-        <v>90529</v>
+        <v>5166</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1976,25 +1991,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624179</v>
+        <v>624103</v>
       </c>
       <c r="R14" t="n">
-        <v>7306747</v>
+        <v>7306727</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,6 +2065,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Under bark på död ved</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Under bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2066,10 +2101,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118925785</v>
+        <v>118927009</v>
       </c>
       <c r="B15" t="n">
-        <v>79572</v>
+        <v>74603</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2082,21 +2117,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624100</v>
+        <v>624137</v>
       </c>
       <c r="R15" t="n">
-        <v>7306706</v>
+        <v>7306972</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,26 +2187,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2188,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118926111</v>
+        <v>118925633</v>
       </c>
       <c r="B16" t="n">
-        <v>57306</v>
+        <v>79476</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,43 +2215,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624121</v>
+        <v>624087</v>
       </c>
       <c r="R16" t="n">
-        <v>7306730</v>
+        <v>7306680</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118925102</v>
+        <v>118927553</v>
       </c>
       <c r="B17" t="n">
-        <v>79080</v>
+        <v>90529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624207</v>
+        <v>624179</v>
       </c>
       <c r="R17" t="n">
-        <v>7306638</v>
+        <v>7306747</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,26 +2391,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2417,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118926450</v>
+        <v>118927732</v>
       </c>
       <c r="B18" t="n">
-        <v>57290</v>
+        <v>91288</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2429,43 +2419,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>918</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624139</v>
+        <v>624261</v>
       </c>
       <c r="R18" t="n">
-        <v>7306755</v>
+        <v>7306731</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,6 +2493,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2524,7 +2529,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118925985</v>
+        <v>118927219</v>
       </c>
       <c r="B19" t="n">
         <v>90529</v>
@@ -2564,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624097</v>
+        <v>624245</v>
       </c>
       <c r="R19" t="n">
-        <v>7306712</v>
+        <v>7306978</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118927259</v>
+        <v>118925985</v>
       </c>
       <c r="B20" t="n">
-        <v>90476</v>
+        <v>90529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2638,25 +2643,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2666,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624213</v>
+        <v>624097</v>
       </c>
       <c r="R20" t="n">
-        <v>7306954</v>
+        <v>7306712</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,26 +2717,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2748,7 +2733,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118927041</v>
+        <v>118926085</v>
       </c>
       <c r="B21" t="n">
         <v>90529</v>
@@ -2788,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624109</v>
+        <v>624103</v>
       </c>
       <c r="R21" t="n">
-        <v>7306964</v>
+        <v>7306730</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118927219</v>
+        <v>118926450</v>
       </c>
       <c r="B22" t="n">
-        <v>90529</v>
+        <v>57290</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2866,34 +2851,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624245</v>
+        <v>624139</v>
       </c>
       <c r="R22" t="n">
-        <v>7306978</v>
+        <v>7306755</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118925708</v>
+        <v>118927329</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
+        <v>77423</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2964,25 +2954,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2992,10 +2982,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624120</v>
+        <v>624174</v>
       </c>
       <c r="R23" t="n">
-        <v>7306680</v>
+        <v>7306885</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3041,22 +3031,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3176,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118927701</v>
+        <v>118927118</v>
       </c>
       <c r="B25" t="n">
-        <v>90565</v>
+        <v>90437</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,21 +3182,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3277</v>
+        <v>3242</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3216,10 +3206,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624205</v>
+        <v>624237</v>
       </c>
       <c r="R25" t="n">
-        <v>7306715</v>
+        <v>7306993</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3278,7 +3268,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118925978</v>
+        <v>118926332</v>
       </c>
       <c r="B26" t="n">
         <v>57290</v>
@@ -3323,10 +3313,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624097</v>
+        <v>624131</v>
       </c>
       <c r="R26" t="n">
-        <v>7306712</v>
+        <v>7306764</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3385,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118926687</v>
+        <v>118925785</v>
       </c>
       <c r="B27" t="n">
-        <v>82270</v>
+        <v>79572</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3401,21 +3391,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3425,10 +3415,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>624121</v>
+        <v>624100</v>
       </c>
       <c r="R27" t="n">
-        <v>7306811</v>
+        <v>7306706</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,6 +3461,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3487,10 +3497,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118926085</v>
+        <v>118927143</v>
       </c>
       <c r="B28" t="n">
-        <v>90529</v>
+        <v>57290</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3503,34 +3513,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>624103</v>
+        <v>624210</v>
       </c>
       <c r="R28" t="n">
-        <v>7306730</v>
+        <v>7306965</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,10 +3604,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118925874</v>
+        <v>118927591</v>
       </c>
       <c r="B29" t="n">
-        <v>82270</v>
+        <v>90529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3605,21 +3620,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3629,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>624111</v>
+        <v>624178</v>
       </c>
       <c r="R29" t="n">
-        <v>7306711</v>
+        <v>7306745</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,26 +3690,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3711,10 +3706,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118925929</v>
+        <v>118927351</v>
       </c>
       <c r="B30" t="n">
-        <v>74603</v>
+        <v>79080</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3727,21 +3722,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3751,10 +3746,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>624109</v>
+        <v>624174</v>
       </c>
       <c r="R30" t="n">
-        <v>7306708</v>
+        <v>7306885</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3797,26 +3792,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3833,10 +3808,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118926985</v>
+        <v>118926301</v>
       </c>
       <c r="B31" t="n">
-        <v>78491</v>
+        <v>77428</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3849,21 +3824,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3873,10 +3848,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>624122</v>
+        <v>624125</v>
       </c>
       <c r="R31" t="n">
-        <v>7306979</v>
+        <v>7306753</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3919,6 +3894,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3935,10 +3930,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118926947</v>
+        <v>118926173</v>
       </c>
       <c r="B32" t="n">
-        <v>78136</v>
+        <v>74603</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3951,21 +3946,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3975,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>624110</v>
+        <v>624111</v>
       </c>
       <c r="R32" t="n">
-        <v>7306963</v>
+        <v>7306730</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4021,26 +4016,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4057,7 +4032,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118927645</v>
+        <v>118925162</v>
       </c>
       <c r="B33" t="n">
         <v>90529</v>
@@ -4097,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>624195</v>
+        <v>624198</v>
       </c>
       <c r="R33" t="n">
-        <v>7306733</v>
+        <v>7306606</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,10 +4134,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118925162</v>
+        <v>118925978</v>
       </c>
       <c r="B34" t="n">
-        <v>90529</v>
+        <v>57290</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4175,34 +4150,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>624198</v>
+        <v>624097</v>
       </c>
       <c r="R34" t="n">
-        <v>7306606</v>
+        <v>7306712</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4261,10 +4241,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118926148</v>
+        <v>118925102</v>
       </c>
       <c r="B35" t="n">
-        <v>5166</v>
+        <v>79080</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4273,25 +4253,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4301,10 +4281,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>624103</v>
+        <v>624207</v>
       </c>
       <c r="R35" t="n">
-        <v>7306727</v>
+        <v>7306638</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4350,22 +4330,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Under bark på död ved</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Under bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4383,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118924931</v>
+        <v>118926697</v>
       </c>
       <c r="B36" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4399,21 +4379,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4423,10 +4403,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>624243</v>
+        <v>624122</v>
       </c>
       <c r="R36" t="n">
-        <v>7306648</v>
+        <v>7306805</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4469,26 +4449,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4505,10 +4465,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118927732</v>
+        <v>118926932</v>
       </c>
       <c r="B37" t="n">
-        <v>91288</v>
+        <v>90437</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4517,25 +4477,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>918</v>
+        <v>3242</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4545,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>624261</v>
+        <v>624112</v>
       </c>
       <c r="R37" t="n">
-        <v>7306731</v>
+        <v>7306964</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4594,22 +4554,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4627,10 +4587,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118926301</v>
+        <v>118927701</v>
       </c>
       <c r="B38" t="n">
-        <v>77428</v>
+        <v>90565</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4643,21 +4603,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>3277</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4667,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>624125</v>
+        <v>624205</v>
       </c>
       <c r="R38" t="n">
-        <v>7306753</v>
+        <v>7306715</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4713,26 +4673,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4749,10 +4689,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118926894</v>
+        <v>118925708</v>
       </c>
       <c r="B39" t="n">
-        <v>79109</v>
+        <v>79607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4761,25 +4701,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4789,10 +4729,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>624140</v>
+        <v>624120</v>
       </c>
       <c r="R39" t="n">
-        <v>7306929</v>
+        <v>7306680</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4835,6 +4775,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4851,10 +4811,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118927605</v>
+        <v>118925929</v>
       </c>
       <c r="B40" t="n">
-        <v>79109</v>
+        <v>74603</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4867,21 +4827,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4891,10 +4851,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>624181</v>
+        <v>624109</v>
       </c>
       <c r="R40" t="n">
-        <v>7306734</v>
+        <v>7306708</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4937,6 +4897,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4953,10 +4933,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118927009</v>
+        <v>118926894</v>
       </c>
       <c r="B41" t="n">
-        <v>74603</v>
+        <v>79109</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4969,21 +4949,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4993,10 +4973,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>624137</v>
+        <v>624140</v>
       </c>
       <c r="R41" t="n">
-        <v>7306972</v>
+        <v>7306929</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5055,10 +5035,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118927825</v>
+        <v>118926985</v>
       </c>
       <c r="B42" t="n">
-        <v>90529</v>
+        <v>78491</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5071,21 +5051,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5095,10 +5075,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>624272</v>
+        <v>624122</v>
       </c>
       <c r="R42" t="n">
-        <v>7306822</v>
+        <v>7306979</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5157,10 +5137,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118926932</v>
+        <v>118924931</v>
       </c>
       <c r="B43" t="n">
-        <v>90437</v>
+        <v>79109</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5173,21 +5153,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5197,10 +5177,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>624112</v>
+        <v>624243</v>
       </c>
       <c r="R43" t="n">
-        <v>7306964</v>
+        <v>7306648</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5279,10 +5259,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118927343</v>
+        <v>118926047</v>
       </c>
       <c r="B44" t="n">
-        <v>77875</v>
+        <v>82270</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5295,21 +5275,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5319,10 +5299,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>624174</v>
+        <v>624098</v>
       </c>
       <c r="R44" t="n">
-        <v>7306885</v>
+        <v>7306733</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5365,26 +5345,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5401,10 +5361,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118926697</v>
+        <v>118926111</v>
       </c>
       <c r="B45" t="n">
-        <v>78491</v>
+        <v>57306</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5417,34 +5377,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>624122</v>
+        <v>624121</v>
       </c>
       <c r="R45" t="n">
-        <v>7306805</v>
+        <v>7306730</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5503,10 +5468,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118927351</v>
+        <v>118926458</v>
       </c>
       <c r="B46" t="n">
-        <v>79080</v>
+        <v>90525</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5519,21 +5484,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5543,10 +5508,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>624174</v>
+        <v>624138</v>
       </c>
       <c r="R46" t="n">
-        <v>7306885</v>
+        <v>7306761</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5589,6 +5554,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5605,10 +5590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118925633</v>
+        <v>118927078</v>
       </c>
       <c r="B47" t="n">
-        <v>79476</v>
+        <v>90529</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5617,25 +5602,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5645,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>624087</v>
+        <v>624160</v>
       </c>
       <c r="R47" t="n">
-        <v>7306680</v>
+        <v>7306966</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5707,10 +5692,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118926332</v>
+        <v>118926947</v>
       </c>
       <c r="B48" t="n">
-        <v>57290</v>
+        <v>78136</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5723,39 +5708,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>624131</v>
+        <v>624110</v>
       </c>
       <c r="R48" t="n">
-        <v>7306764</v>
+        <v>7306963</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5798,6 +5778,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 64817-2023 artfynd.xlsx
+++ b/artfynd/A 64817-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118925866</v>
+        <v>118926947</v>
       </c>
       <c r="B2" t="n">
-        <v>78575</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624097</v>
+        <v>624110</v>
       </c>
       <c r="R2" t="n">
-        <v>7306720</v>
+        <v>7306963</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,22 +759,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118927329</v>
+        <v>118925866</v>
       </c>
       <c r="B3" t="n">
-        <v>77425</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624174</v>
+        <v>624097</v>
       </c>
       <c r="R3" t="n">
-        <v>7306885</v>
+        <v>7306720</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,22 +876,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,50 +909,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118927219</v>
+        <v>118927732</v>
       </c>
       <c r="B4" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624245</v>
+        <v>624261</v>
       </c>
       <c r="R4" t="n">
-        <v>7306978</v>
+        <v>7306731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,6 +990,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,50 +1026,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118926085</v>
+        <v>118926458</v>
       </c>
       <c r="B5" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624103</v>
+        <v>624138</v>
       </c>
       <c r="R5" t="n">
-        <v>7306730</v>
+        <v>7306761</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,6 +1107,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1123,15 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118926826</v>
+        <v>118925874</v>
       </c>
       <c r="B6" t="n">
-        <v>79111</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624134</v>
+        <v>624111</v>
       </c>
       <c r="R6" t="n">
-        <v>7306829</v>
+        <v>7306711</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,6 +1224,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1225,15 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118927825</v>
+        <v>118926047</v>
       </c>
       <c r="B7" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,34 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624272</v>
+        <v>624098</v>
       </c>
       <c r="R7" t="n">
-        <v>7306822</v>
+        <v>7306733</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,15 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118927118</v>
+        <v>118926687</v>
       </c>
       <c r="B8" t="n">
-        <v>90439</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,34 +1368,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624237</v>
+        <v>624121</v>
       </c>
       <c r="R8" t="n">
-        <v>7306993</v>
+        <v>7306811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,15 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118925874</v>
+        <v>118926932</v>
       </c>
       <c r="B9" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,34 +1465,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624111</v>
+        <v>624112</v>
       </c>
       <c r="R9" t="n">
-        <v>7306711</v>
+        <v>7306964</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,22 +1538,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1551,15 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118927143</v>
+        <v>118927118</v>
       </c>
       <c r="B10" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,39 +1582,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624210</v>
+        <v>624237</v>
       </c>
       <c r="R10" t="n">
-        <v>7306965</v>
+        <v>7306993</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,15 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118925929</v>
+        <v>118927701</v>
       </c>
       <c r="B11" t="n">
-        <v>74605</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,34 +1679,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>3277</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624109</v>
+        <v>624205</v>
       </c>
       <c r="R11" t="n">
-        <v>7306708</v>
+        <v>7306715</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,26 +1749,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1780,50 +1765,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118926458</v>
+        <v>118927259</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624138</v>
+        <v>624213</v>
       </c>
       <c r="R12" t="n">
-        <v>7306761</v>
+        <v>7306954</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,12 +1849,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -1884,7 +1864,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1902,15 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118927732</v>
+        <v>118926697</v>
       </c>
       <c r="B13" t="n">
-        <v>91290</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,34 +1893,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>918</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624261</v>
+        <v>624122</v>
       </c>
       <c r="R13" t="n">
-        <v>7306731</v>
+        <v>7306805</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1988,26 +1963,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2024,50 +1979,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118925679</v>
+        <v>118926985</v>
       </c>
       <c r="B14" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624112</v>
+        <v>624122</v>
       </c>
       <c r="R14" t="n">
-        <v>7306697</v>
+        <v>7306979</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,15 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118927078</v>
+        <v>118927343</v>
       </c>
       <c r="B15" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,34 +2087,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624160</v>
+        <v>624174</v>
       </c>
       <c r="R15" t="n">
-        <v>7306966</v>
+        <v>7306885</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,6 +2157,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2228,15 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118924931</v>
+        <v>118925929</v>
       </c>
       <c r="B16" t="n">
-        <v>79111</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,34 +2204,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624243</v>
+        <v>624109</v>
       </c>
       <c r="R16" t="n">
-        <v>7306648</v>
+        <v>7306708</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,22 +2277,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,15 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118926047</v>
+        <v>118926173</v>
       </c>
       <c r="B17" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,34 +2321,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624098</v>
+        <v>624111</v>
       </c>
       <c r="R17" t="n">
-        <v>7306733</v>
+        <v>7306730</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,50 +2407,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118926148</v>
+        <v>118927009</v>
       </c>
       <c r="B18" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624103</v>
+        <v>624137</v>
       </c>
       <c r="R18" t="n">
-        <v>7306727</v>
+        <v>7306972</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2538,26 +2488,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Under bark på död ved</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Under bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2574,15 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118926947</v>
+        <v>118924931</v>
       </c>
       <c r="B19" t="n">
-        <v>78138</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,34 +2515,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624110</v>
+        <v>624243</v>
       </c>
       <c r="R19" t="n">
-        <v>7306963</v>
+        <v>7306648</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,50 +2621,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118925633</v>
+        <v>118926826</v>
       </c>
       <c r="B20" t="n">
-        <v>79478</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624087</v>
+        <v>624134</v>
       </c>
       <c r="R20" t="n">
-        <v>7306680</v>
+        <v>7306829</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2798,50 +2718,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118927259</v>
+        <v>118926894</v>
       </c>
       <c r="B21" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624213</v>
+        <v>624140</v>
       </c>
       <c r="R21" t="n">
-        <v>7306954</v>
+        <v>7306929</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2884,26 +2799,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2920,15 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118926111</v>
+        <v>118927605</v>
       </c>
       <c r="B22" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,39 +2826,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624121</v>
+        <v>624181</v>
       </c>
       <c r="R22" t="n">
-        <v>7306730</v>
+        <v>7306734</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,50 +2912,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118927009</v>
+        <v>118925331</v>
       </c>
       <c r="B23" t="n">
-        <v>74605</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624137</v>
+        <v>624077</v>
       </c>
       <c r="R23" t="n">
-        <v>7306972</v>
+        <v>7306658</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3113,6 +2993,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3129,50 +3029,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118926697</v>
+        <v>118925633</v>
       </c>
       <c r="B24" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624122</v>
+        <v>624087</v>
       </c>
       <c r="R24" t="n">
-        <v>7306805</v>
+        <v>7306680</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,15 +3126,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118927591</v>
+        <v>118925785</v>
       </c>
       <c r="B25" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3247,34 +3137,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>624178</v>
+        <v>624100</v>
       </c>
       <c r="R25" t="n">
-        <v>7306745</v>
+        <v>7306706</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3317,6 +3207,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3333,50 +3243,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118926894</v>
+        <v>118925708</v>
       </c>
       <c r="B26" t="n">
-        <v>79111</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>624140</v>
+        <v>624120</v>
       </c>
       <c r="R26" t="n">
-        <v>7306929</v>
+        <v>7306680</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3419,6 +3324,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3435,15 +3360,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118926932</v>
+        <v>118927329</v>
       </c>
       <c r="B27" t="n">
-        <v>90439</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3451,34 +3371,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3242</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>624112</v>
+        <v>624174</v>
       </c>
       <c r="R27" t="n">
-        <v>7306964</v>
+        <v>7306885</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3557,50 +3477,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118927701</v>
+        <v>118926111</v>
       </c>
       <c r="B28" t="n">
-        <v>90567</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3277</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>624205</v>
+        <v>624121</v>
       </c>
       <c r="R28" t="n">
-        <v>7306715</v>
+        <v>7306730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3662,12 +3582,7 @@
         <v>118925978</v>
       </c>
       <c r="B29" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3700,7 +3615,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -3766,15 +3681,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118926985</v>
+        <v>118926332</v>
       </c>
       <c r="B30" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,34 +3692,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>624122</v>
+        <v>624131</v>
       </c>
       <c r="R30" t="n">
-        <v>7306979</v>
+        <v>7306764</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3871,12 +3786,7 @@
         <v>118926450</v>
       </c>
       <c r="B31" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3909,7 +3819,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -3975,15 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118925785</v>
+        <v>118927143</v>
       </c>
       <c r="B32" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3991,34 +3896,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>624100</v>
+        <v>624210</v>
       </c>
       <c r="R32" t="n">
-        <v>7306706</v>
+        <v>7306965</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4061,26 +3971,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4097,50 +3987,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118927553</v>
+        <v>118926148</v>
       </c>
       <c r="B33" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>624179</v>
+        <v>624103</v>
       </c>
       <c r="R33" t="n">
-        <v>7306747</v>
+        <v>7306727</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4183,6 +4068,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Under bark på död ved</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Under bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4199,50 +4104,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118925162</v>
+        <v>118926360</v>
       </c>
       <c r="B34" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>624198</v>
+        <v>624137</v>
       </c>
       <c r="R34" t="n">
-        <v>7306606</v>
+        <v>7306757</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4301,15 +4201,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118927343</v>
+        <v>118926301</v>
       </c>
       <c r="B35" t="n">
-        <v>77877</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4317,34 +4212,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>624174</v>
+        <v>624125</v>
       </c>
       <c r="R35" t="n">
-        <v>7306885</v>
+        <v>7306753</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4390,22 +4285,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4423,50 +4318,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118925708</v>
+        <v>118925102</v>
       </c>
       <c r="B36" t="n">
-        <v>79609</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>624120</v>
+        <v>624207</v>
       </c>
       <c r="R36" t="n">
-        <v>7306680</v>
+        <v>7306638</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4512,22 +4402,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4545,15 +4435,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118927605</v>
+        <v>118927351</v>
       </c>
       <c r="B37" t="n">
-        <v>79111</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4561,34 +4446,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
+          <t>Fäbodsjön, Fäbodsjön, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>624181</v>
+        <v>624174</v>
       </c>
       <c r="R37" t="n">
-        <v>7306734</v>
+        <v>7306885</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4644,1173 +4529,6 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>118926687</v>
-      </c>
-      <c r="B38" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>624121</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7306811</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>118926360</v>
-      </c>
-      <c r="B39" t="n">
-        <v>104937</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>221725</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>624137</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7306757</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>118927041</v>
-      </c>
-      <c r="B40" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>624109</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7306964</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>118927351</v>
-      </c>
-      <c r="B41" t="n">
-        <v>79082</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>624174</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7306885</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>118926301</v>
-      </c>
-      <c r="B42" t="n">
-        <v>77430</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>624125</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7306753</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>118927645</v>
-      </c>
-      <c r="B43" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>624195</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7306733</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>118925985</v>
-      </c>
-      <c r="B44" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>624097</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7306712</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>118925102</v>
-      </c>
-      <c r="B45" t="n">
-        <v>79082</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>624207</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7306638</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>118926173</v>
-      </c>
-      <c r="B46" t="n">
-        <v>74605</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>624111</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7306730</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>118925261</v>
-      </c>
-      <c r="B47" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>624125</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7306711</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>118926332</v>
-      </c>
-      <c r="B48" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Fäbodsjön (Fäbodsjön), Pi lm</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>624131</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7306764</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64817-2023 artfynd.xlsx
+++ b/artfynd/A 64817-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926947</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118925866</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118927732</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926458</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118925874</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1354,6 +1384,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926047</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926687</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926932</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1665,6 +1710,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118927118</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118927701</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118927259</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926697</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926985</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2190,6 +2260,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118927343</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2307,6 +2382,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118925929</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2404,6 +2484,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926173</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2501,6 +2586,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118927009</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2618,6 +2708,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118924931</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2715,6 +2810,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926826</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926894</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2909,6 +3014,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118927605</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118925331</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3123,6 +3238,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118925633</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118925785</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3357,6 +3482,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118925708</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3474,6 +3604,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118927329</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3576,6 +3711,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926111</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3678,6 +3818,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118925978</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3780,6 +3925,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926332</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,6 +4032,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926450</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3984,6 +4139,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118927143</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4101,6 +4261,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926148</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4198,6 +4363,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926360</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4315,6 +4485,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118926301</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4432,6 +4607,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118925102</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4529,8 +4709,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118927351</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>